--- a/Curs Oficial/sesiuni/s05/echipa_galben/Produse.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_galben/Produse.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Produse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
         <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>4.57</v>
+        <v>25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.31</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>89</v>
       </c>
       <c r="H6" t="n">
-        <v>5.98</v>
+        <v>7.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>245</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>21</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45</v>
       </c>
       <c r="H9" t="n">
-        <v>5.27</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>399</v>
       </c>
       <c r="H10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -813,7 +813,6 @@
           <t xml:space="preserve">  Nivel laser  </t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Masura</t>
@@ -828,7 +827,7 @@
         <v>289</v>
       </c>
       <c r="H11" t="n">
-        <v>5.56</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -869,7 +868,7 @@
         <v>42</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>1.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -910,7 +909,7 @@
         <v>38</v>
       </c>
       <c r="H13" t="n">
-        <v>7.27</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -949,7 +948,7 @@
         <v>55</v>
       </c>
       <c r="H14" t="n">
-        <v>11.04</v>
+        <v>2.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -990,7 +989,7 @@
         <v>120</v>
       </c>
       <c r="H15" t="n">
-        <v>3.19</v>
+        <v>9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1031,7 +1030,7 @@
         <v>159</v>
       </c>
       <c r="H16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1072,7 +1071,7 @@
         <v>1890</v>
       </c>
       <c r="H17" t="n">
-        <v>6.26</v>
+        <v>68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1113,7 +1112,7 @@
         <v>72</v>
       </c>
       <c r="H18" t="n">
-        <v>7.72</v>
+        <v>18</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1154,7 +1153,7 @@
         <v>24</v>
       </c>
       <c r="H19" t="n">
-        <v>6.23</v>
+        <v>0.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1195,7 +1194,7 @@
         <v>189</v>
       </c>
       <c r="H20" t="n">
-        <v>3.64</v>
+        <v>1.2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1236,7 +1235,7 @@
         <v>15</v>
       </c>
       <c r="H21" t="n">
-        <v>2.61</v>
+        <v>8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1250,14 +1249,6 @@
           <t>Categorii: fill-down manual daca lipseste</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
